--- a/Results/Chemical industry emissions.xlsx
+++ b/Results/Chemical industry emissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8DB7F00-81C4-492F-B5FC-E33CFB738BEC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC9443F-D6B4-4799-8C91-079C9BE6E429}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="1" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Results/Chemical industry emissions.xlsx
+++ b/Results/Chemical industry emissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC9443F-D6B4-4799-8C91-079C9BE6E429}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E8AA89-B712-4D4E-BDFE-3262E01DEE3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="1" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -462,7 +462,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA46F0FD-6844-48BF-9AEE-5AB510430A25}">
-  <dimension ref="A1:L15"/>
+  <dimension ref="A1:L20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -642,6 +642,9 @@
         <v>12</v>
       </c>
     </row>
+    <row r="20" spans="8:8" x14ac:dyDescent="0.25">
+      <c r="H20" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -649,15 +652,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AF0455-819B-47A2-B85B-CBE39F93F536}">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="11.5703125" style="10" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="12.28515625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="10"/>
+    <col min="7" max="9" width="9.140625" style="10"/>
+    <col min="10" max="10" width="10.5703125" style="10" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="13">
         <f>Sheet1!B6</f>
         <v>2052</v>
@@ -674,10 +679,13 @@
         <f>C1+Sheet1!B4</f>
         <v>3140.5905511811025</v>
       </c>
-      <c r="E1" s="12"/>
+      <c r="E1" s="12">
+        <f>D1+A2+B2+C2+D2</f>
+        <v>4104</v>
+      </c>
       <c r="F1" s="12"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="12">
         <f>A1</f>
         <v>2052</v>
@@ -694,10 +702,13 @@
         <f>-Sheet1!B4</f>
         <v>-182</v>
       </c>
-      <c r="E2" s="12"/>
+      <c r="E2" s="12">
+        <f>-SUM(A2:D2)</f>
+        <v>-963.40944881889777</v>
+      </c>
       <c r="F2" s="12"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="12">
         <v>0</v>
       </c>
@@ -713,10 +724,13 @@
         <f>C3+C2</f>
         <v>1145.4094488188978</v>
       </c>
-      <c r="E3" s="12"/>
+      <c r="E3" s="12">
+        <f>D2+D3</f>
+        <v>963.40944881889777</v>
+      </c>
       <c r="F3" s="12"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="11"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -724,6 +738,9 @@
       <c r="E4" s="11"/>
       <c r="F4" s="11"/>
     </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7" s="12"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Results/Chemical industry emissions.xlsx
+++ b/Results/Chemical industry emissions.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20403"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74E8AA89-B712-4D4E-BDFE-3262E01DEE3E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A63116-758E-4A56-B7E9-B3B3EF4F2CA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="1" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="2" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Waterfall final data" sheetId="2" r:id="rId2"/>
+    <sheet name="Figure 1" sheetId="3" r:id="rId3"/>
+    <sheet name="Emissions 2050" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -26,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
   <si>
     <t>Emissions</t>
   </si>
@@ -71,6 +73,63 @@
   </si>
   <si>
     <t>https://doi.org/10.1016/j.oneear.2023.05.006</t>
+  </si>
+  <si>
+    <t>Hydrogen</t>
+  </si>
+  <si>
+    <t>Demand 2020</t>
+  </si>
+  <si>
+    <t>Emissions 2020</t>
+  </si>
+  <si>
+    <t>Demand 2050</t>
+  </si>
+  <si>
+    <t>Emissions 2050</t>
+  </si>
+  <si>
+    <t>Emissions 2050 low</t>
+  </si>
+  <si>
+    <t>Emissions 2050 high</t>
+  </si>
+  <si>
+    <t>Chemical</t>
+  </si>
+  <si>
+    <t>Average</t>
+  </si>
+  <si>
+    <t>Minimum</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>Wind RCP6</t>
+  </si>
+  <si>
+    <t>Wind RCP19</t>
+  </si>
+  <si>
+    <t>Wind RCP26</t>
+  </si>
+  <si>
+    <t>Solar RCP6</t>
+  </si>
+  <si>
+    <t>Solar RCP19</t>
+  </si>
+  <si>
+    <t>Solar RCP26</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Dummy</t>
   </si>
 </sst>
 </file>
@@ -82,7 +141,7 @@
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -96,6 +155,14 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -113,7 +180,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -121,12 +188,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -147,6 +229,24 @@
     <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -744,4 +844,310 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C001277B-28C9-4CD9-96D9-6BE2F8B84795}">
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="16" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="14">
+        <v>100</v>
+      </c>
+      <c r="C2" s="15">
+        <v>89</v>
+      </c>
+      <c r="D2" s="14">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="14">
+        <v>182</v>
+      </c>
+      <c r="C3" s="14">
+        <v>457</v>
+      </c>
+      <c r="D3" s="14">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="14">
+        <v>0</v>
+      </c>
+      <c r="C4" s="14">
+        <v>0</v>
+      </c>
+      <c r="D4" s="14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="15">
+        <f>B2*5</f>
+        <v>500</v>
+      </c>
+      <c r="C5" s="15">
+        <f>C2*5</f>
+        <v>445</v>
+      </c>
+      <c r="D5" s="14">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="15">
+        <f>B5*'Emissions 2050'!E9</f>
+        <v>-592.15017899385589</v>
+      </c>
+      <c r="C6" s="15">
+        <f>C5*'Emissions 2050'!C9</f>
+        <v>789.1398488144074</v>
+      </c>
+      <c r="D6" s="15">
+        <f>D5*'Emissions 2050'!D9</f>
+        <v>164.79216746574841</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="15">
+        <f>B5*'Emissions 2050'!E10</f>
+        <v>-685.58569963752905</v>
+      </c>
+      <c r="C7" s="15">
+        <f>C5*'Emissions 2050'!C10</f>
+        <v>513.55728461101455</v>
+      </c>
+      <c r="D7" s="15">
+        <f>D5*'Emissions 2050'!D10</f>
+        <v>86.075948957690926</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="15">
+        <f>B5*'Emissions 2050'!E11</f>
+        <v>-437.70406457422655</v>
+      </c>
+      <c r="C8" s="15">
+        <f>C5*'Emissions 2050'!C11</f>
+        <v>1218.752561613959</v>
+      </c>
+      <c r="D8" s="15">
+        <f>D5*'Emissions 2050'!D11</f>
+        <v>300.25167049638441</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE43E8DA-9867-4BC9-A414-3C21550121EB}">
+  <dimension ref="B2:E11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="17">
+        <v>1.8971083255038561</v>
+      </c>
+      <c r="D3" s="17">
+        <v>0.69764693455946902</v>
+      </c>
+      <c r="E3" s="17">
+        <v>-0.99237845448159656</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="17">
+        <v>1.154061313732617</v>
+      </c>
+      <c r="D4" s="17">
+        <v>0.2424674618526505</v>
+      </c>
+      <c r="E4" s="17">
+        <v>-1.371171399275058</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="17">
+        <v>1.322298040883372</v>
+      </c>
+      <c r="D5" s="17">
+        <v>0.28589805137132751</v>
+      </c>
+      <c r="E5" s="17">
+        <v>-1.320902128073866</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="17">
+        <v>2.7387698013796831</v>
+      </c>
+      <c r="D6" s="17">
+        <v>0.84577935351094191</v>
+      </c>
+      <c r="E6" s="17">
+        <v>-0.87540812914845312</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="17">
+        <v>1.6775179614556699</v>
+      </c>
+      <c r="D7" s="17">
+        <v>0.3345958313526991</v>
+      </c>
+      <c r="E7" s="17">
+        <v>-1.2984237493742981</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="17">
+        <v>1.850332406227821</v>
+      </c>
+      <c r="D8" s="17">
+        <v>0.37883209916837801</v>
+      </c>
+      <c r="E8" s="17">
+        <v>-1.2475182875729991</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" s="18">
+        <f>AVERAGE(C3:C8)</f>
+        <v>1.7733479748638368</v>
+      </c>
+      <c r="D9" s="18">
+        <f>AVERAGE(D3:D8)</f>
+        <v>0.46420328863591104</v>
+      </c>
+      <c r="E9" s="18">
+        <f>AVERAGE(E3:E8)</f>
+        <v>-1.1843003579877118</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="18">
+        <f>MIN(C3:C8)</f>
+        <v>1.154061313732617</v>
+      </c>
+      <c r="D10" s="18">
+        <f>MIN(D3:D8)</f>
+        <v>0.2424674618526505</v>
+      </c>
+      <c r="E10" s="18">
+        <f>MIN(E3:E8)</f>
+        <v>-1.371171399275058</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="18">
+        <f>MAX(C3:C8)</f>
+        <v>2.7387698013796831</v>
+      </c>
+      <c r="D11" s="18">
+        <f>MAX(D3:D8)</f>
+        <v>0.84577935351094191</v>
+      </c>
+      <c r="E11" s="18">
+        <f>MAX(E3:E8)</f>
+        <v>-0.87540812914845312</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Results/Chemical industry emissions.xlsx
+++ b/Results/Chemical industry emissions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20405"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73A63116-758E-4A56-B7E9-B3B3EF4F2CA5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C14E30-2B3F-4D89-9321-1FE7BE06F2AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="2" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
   </bookViews>
@@ -890,16 +890,18 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B3" s="14">
-        <v>182</v>
-      </c>
-      <c r="C3" s="14">
-        <v>457</v>
+        <v>18</v>
+      </c>
+      <c r="B3" s="15">
+        <f>B2*5</f>
+        <v>500</v>
+      </c>
+      <c r="C3" s="15">
+        <f>C2*5</f>
+        <v>445</v>
       </c>
       <c r="D3" s="14">
-        <v>450</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -918,18 +920,16 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="15">
-        <f>B2*5</f>
-        <v>500</v>
-      </c>
-      <c r="C5" s="15">
-        <f>C2*5</f>
-        <v>445</v>
+        <v>17</v>
+      </c>
+      <c r="B5" s="14">
+        <v>182</v>
+      </c>
+      <c r="C5" s="14">
+        <v>457</v>
       </c>
       <c r="D5" s="14">
-        <v>355</v>
+        <v>450</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -937,15 +937,15 @@
         <v>19</v>
       </c>
       <c r="B6" s="15">
-        <f>B5*'Emissions 2050'!E9</f>
+        <f>B3*'Emissions 2050'!E9</f>
         <v>-592.15017899385589</v>
       </c>
       <c r="C6" s="15">
-        <f>C5*'Emissions 2050'!C9</f>
+        <f>C3*'Emissions 2050'!C9</f>
         <v>789.1398488144074</v>
       </c>
       <c r="D6" s="15">
-        <f>D5*'Emissions 2050'!D9</f>
+        <f>D3*'Emissions 2050'!D9</f>
         <v>164.79216746574841</v>
       </c>
     </row>
@@ -954,15 +954,15 @@
         <v>20</v>
       </c>
       <c r="B7" s="15">
-        <f>B5*'Emissions 2050'!E10</f>
+        <f>B3*'Emissions 2050'!E10</f>
         <v>-685.58569963752905</v>
       </c>
       <c r="C7" s="15">
-        <f>C5*'Emissions 2050'!C10</f>
+        <f>C3*'Emissions 2050'!C10</f>
         <v>513.55728461101455</v>
       </c>
       <c r="D7" s="15">
-        <f>D5*'Emissions 2050'!D10</f>
+        <f>D3*'Emissions 2050'!D10</f>
         <v>86.075948957690926</v>
       </c>
     </row>
@@ -971,15 +971,15 @@
         <v>21</v>
       </c>
       <c r="B8" s="15">
-        <f>B5*'Emissions 2050'!E11</f>
+        <f>B3*'Emissions 2050'!E11</f>
         <v>-437.70406457422655</v>
       </c>
       <c r="C8" s="15">
-        <f>C5*'Emissions 2050'!C11</f>
+        <f>C3*'Emissions 2050'!C11</f>
         <v>1218.752561613959</v>
       </c>
       <c r="D8" s="15">
-        <f>D5*'Emissions 2050'!D11</f>
+        <f>D3*'Emissions 2050'!D11</f>
         <v>300.25167049638441</v>
       </c>
     </row>

--- a/Results/Chemical industry emissions.xlsx
+++ b/Results/Chemical industry emissions.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16C14E30-2B3F-4D89-9321-1FE7BE06F2AC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DB02FF-4034-4BD7-9F19-6FF71FFC5CC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="2" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="3" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -208,7 +208,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -245,6 +245,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1100,15 +1103,15 @@
       <c r="B9" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="18">
+      <c r="C9" s="20">
         <f>AVERAGE(C3:C8)</f>
         <v>1.7733479748638368</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="20">
         <f>AVERAGE(D3:D8)</f>
         <v>0.46420328863591104</v>
       </c>
-      <c r="E9" s="18">
+      <c r="E9" s="20">
         <f>AVERAGE(E3:E8)</f>
         <v>-1.1843003579877118</v>
       </c>

--- a/Results/Chemical industry emissions.xlsx
+++ b/Results/Chemical industry emissions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20405"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20406"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DB02FF-4034-4BD7-9F19-6FF71FFC5CC6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAA58EA-080F-4BA4-AA5E-5566B9F5C6CF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="3" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14025" activeTab="2" xr2:uid="{B97F3159-796F-4D28-AF5A-4DA070CE1984}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="40">
   <si>
     <t>Emissions</t>
   </si>
@@ -78,24 +78,6 @@
     <t>Hydrogen</t>
   </si>
   <si>
-    <t>Demand 2020</t>
-  </si>
-  <si>
-    <t>Emissions 2020</t>
-  </si>
-  <si>
-    <t>Demand 2050</t>
-  </si>
-  <si>
-    <t>Emissions 2050</t>
-  </si>
-  <si>
-    <t>Emissions 2050 low</t>
-  </si>
-  <si>
-    <t>Emissions 2050 high</t>
-  </si>
-  <si>
     <t>Chemical</t>
   </si>
   <si>
@@ -130,6 +112,42 @@
   </si>
   <si>
     <t>Dummy</t>
+  </si>
+  <si>
+    <t>Fossil 2020</t>
+  </si>
+  <si>
+    <t>Fossil 2050</t>
+  </si>
+  <si>
+    <t>Green 2020</t>
+  </si>
+  <si>
+    <t>Green 2050</t>
+  </si>
+  <si>
+    <t>Fossil RCP6</t>
+  </si>
+  <si>
+    <t>Fossil RCP19</t>
+  </si>
+  <si>
+    <t>Fossil RCP26</t>
+  </si>
+  <si>
+    <t>demand</t>
+  </si>
+  <si>
+    <t>methanol</t>
+  </si>
+  <si>
+    <t>hydrogen</t>
+  </si>
+  <si>
+    <t>ammonia</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -180,7 +198,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -203,12 +221,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -248,6 +275,22 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -565,7 +608,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA46F0FD-6844-48BF-9AEE-5AB510430A25}">
-  <dimension ref="A1:L20"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -574,12 +617,12 @@
     <col min="11" max="11" width="6.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>0</v>
       </c>
@@ -593,7 +636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -625,7 +668,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -657,7 +700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -681,8 +724,17 @@
         <f>H5*$G$10/100</f>
         <v>162.63779527559055</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M5" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" t="s">
+        <v>37</v>
+      </c>
+      <c r="O5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B6">
         <f>B3+B4+B5</f>
         <v>2052</v>
@@ -704,15 +756,48 @@
         <f>H6*$G$10/100</f>
         <v>54.212598425196838</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="22">
+        <v>100</v>
+      </c>
+      <c r="N6" s="22">
+        <v>89</v>
+      </c>
+      <c r="O6" s="22">
+        <v>185</v>
+      </c>
+      <c r="P6" s="24">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="G7" s="2">
         <f>SUM(G3:G6)</f>
         <v>88.9</v>
       </c>
       <c r="H7" s="2"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M7" s="2">
+        <f>M6*5</f>
+        <v>500</v>
+      </c>
+      <c r="N7" s="2">
+        <v>0</v>
+      </c>
+      <c r="O7" s="2">
+        <v>355</v>
+      </c>
+      <c r="P7" s="2">
+        <v>2050</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="M8" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>8</v>
       </c>
@@ -723,13 +808,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="J13" s="1">
         <f>B6-K3</f>
         <v>1595.4094488188978</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>13</v>
       </c>
@@ -737,7 +822,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>11</v>
       </c>
@@ -851,140 +936,95 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C001277B-28C9-4CD9-96D9-6BE2F8B84795}">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="D1" s="16" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="14">
-        <v>100</v>
-      </c>
-      <c r="C2" s="15">
-        <v>89</v>
-      </c>
-      <c r="D2" s="14">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+        <v>28</v>
+      </c>
+      <c r="B2" s="26">
+        <f>Sheet1!M6*'Emissions 2050'!E5</f>
+        <v>76.011638480268701</v>
+      </c>
+      <c r="C2" s="26">
+        <f>Sheet1!O6*'Emissions 2050'!D5</f>
+        <v>499.0848143315074</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B3" s="15">
-        <f>B2*5</f>
-        <v>500</v>
+        <f>Sheet1!M7*'Emissions 2050'!E14</f>
+        <v>350.54776830218714</v>
       </c>
       <c r="C3" s="15">
-        <f>C2*5</f>
-        <v>445</v>
-      </c>
-      <c r="D3" s="14">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <f>Sheet1!O7*'Emissions 2050'!D14</f>
+        <v>929.18878202293115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="14">
+        <v>27</v>
+      </c>
+      <c r="B4" s="15">
         <v>0</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="15">
         <v>0</v>
       </c>
-      <c r="D4" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" s="14">
-        <v>182</v>
-      </c>
-      <c r="C5" s="14">
-        <v>457</v>
-      </c>
-      <c r="D5" s="14">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+      <c r="B5" s="15">
+        <f>Sheet1!M6*'Emissions 2050'!J6</f>
+        <v>-73.389742341651669</v>
+      </c>
+      <c r="C5" s="15">
+        <f>Sheet1!O6*'Emissions 2050'!I6</f>
+        <v>185.04258143923093</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="B6" s="15">
-        <f>B3*'Emissions 2050'!E9</f>
-        <v>-592.15017899385589</v>
+        <f>Sheet1!M7*'Emissions 2050'!J18</f>
+        <v>-592.1501789938676</v>
       </c>
       <c r="C6" s="15">
-        <f>C3*'Emissions 2050'!C9</f>
-        <v>789.1398488144074</v>
-      </c>
-      <c r="D6" s="15">
-        <f>D3*'Emissions 2050'!D9</f>
-        <v>164.79216746574841</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="15">
-        <f>B3*'Emissions 2050'!E10</f>
-        <v>-685.58569963752905</v>
-      </c>
-      <c r="C7" s="15">
-        <f>C3*'Emissions 2050'!C10</f>
-        <v>513.55728461101455</v>
-      </c>
-      <c r="D7" s="15">
-        <f>D3*'Emissions 2050'!D10</f>
-        <v>86.075948957690926</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8" s="15">
-        <f>B3*'Emissions 2050'!E11</f>
-        <v>-437.70406457422655</v>
-      </c>
-      <c r="C8" s="15">
-        <f>C3*'Emissions 2050'!C11</f>
-        <v>1218.752561613959</v>
-      </c>
-      <c r="D8" s="15">
-        <f>D3*'Emissions 2050'!D11</f>
-        <v>300.25167049638441</v>
-      </c>
+        <f>Sheet1!O7*'Emissions 2050'!I18</f>
+        <v>164.79216746574869</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E7" s="23"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -994,163 +1034,459 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE43E8DA-9867-4BC9-A414-3C21550121EB}">
-  <dimension ref="B2:E11"/>
+  <dimension ref="B2:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="21">
+        <v>2020</v>
+      </c>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="G2" s="21">
+        <v>2020</v>
+      </c>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I3" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C4" s="17">
+        <v>11.07977878591611</v>
+      </c>
+      <c r="D4" s="17">
+        <v>2.6977557531432832</v>
+      </c>
+      <c r="E4" s="17">
+        <v>0.76011638480268706</v>
+      </c>
+      <c r="G4" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="17">
+        <v>2.3990751970328539</v>
+      </c>
+      <c r="I4" s="17">
+        <v>0.85375564711232665</v>
+      </c>
+      <c r="J4" s="17">
+        <v>-0.84955861837744795</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="20">
+        <f>AVERAGE(C4:C4)</f>
+        <v>11.07977878591611</v>
+      </c>
+      <c r="D5" s="20">
+        <f>AVERAGE(D4:D4)</f>
+        <v>2.6977557531432832</v>
+      </c>
+      <c r="E5" s="20">
+        <f>AVERAGE(E4:E4)</f>
+        <v>0.76011638480268706</v>
+      </c>
+      <c r="G5" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="17">
+        <v>4.0635584200231838</v>
+      </c>
+      <c r="I5" s="17">
+        <v>1.146704692771251</v>
+      </c>
+      <c r="J5" s="17">
+        <v>-0.61823622845558535</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="18">
+        <f>MIN(C4:C4)</f>
+        <v>11.07977878591611</v>
+      </c>
+      <c r="D6" s="18">
+        <f>MIN(D4:D4)</f>
+        <v>2.6977557531432832</v>
+      </c>
+      <c r="E6" s="18">
+        <f>MIN(E4:E4)</f>
+        <v>0.76011638480268706</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="20">
+        <f>AVERAGE(H4:H5)</f>
+        <v>3.2313168085280188</v>
+      </c>
+      <c r="I6" s="20">
+        <f>AVERAGE(I4:I5)</f>
+        <v>1.0002301699417888</v>
+      </c>
+      <c r="J6" s="20">
+        <f>AVERAGE(J4:J5)</f>
+        <v>-0.73389742341651665</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" s="18">
+        <f>MAX(C4:C4)</f>
+        <v>11.07977878591611</v>
+      </c>
+      <c r="D7" s="18">
+        <f>MAX(D4:D4)</f>
+        <v>2.6977557531432832</v>
+      </c>
+      <c r="E7" s="18">
+        <f>MAX(E4:E4)</f>
+        <v>0.76011638480268706</v>
+      </c>
+      <c r="G7" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="18">
+        <f>MIN(H4:H5)</f>
+        <v>2.3990751970328539</v>
+      </c>
+      <c r="I7" s="18">
+        <f>MIN(I4:I5)</f>
+        <v>0.85375564711232665</v>
+      </c>
+      <c r="J7" s="18">
+        <f>MIN(J4:J5)</f>
+        <v>-0.84955861837744795</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="18">
+        <f>MAX(H4:H5)</f>
+        <v>4.0635584200231838</v>
+      </c>
+      <c r="I8" s="18">
+        <f>MAX(I4:I5)</f>
+        <v>1.146704692771251</v>
+      </c>
+      <c r="J8" s="18">
+        <f>MAX(J4:J5)</f>
+        <v>-0.61823622845558535</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="21">
+        <v>2050</v>
+      </c>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D10" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E10" s="16" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="14" t="s">
+      <c r="G10" s="21">
+        <v>2050</v>
+      </c>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="21"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="17">
+        <v>11.015663193455291</v>
+      </c>
+      <c r="D11" s="17">
+        <v>2.6749031256758502</v>
+      </c>
+      <c r="E11" s="17">
+        <v>0.74348133952478035</v>
+      </c>
+      <c r="G11" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="17">
-        <v>1.8971083255038561</v>
-      </c>
-      <c r="D3" s="17">
-        <v>0.69764693455946902</v>
-      </c>
-      <c r="E3" s="17">
-        <v>-0.99237845448159656</v>
-      </c>
-    </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B4" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="17">
+      <c r="H11" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="I11" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="16" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="17">
+        <v>10.79532945823042</v>
+      </c>
+      <c r="D12" s="17">
+        <v>2.581879576756648</v>
+      </c>
+      <c r="E12" s="17">
+        <v>0.67639002643719903</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="17">
+        <v>1.8971083255038641</v>
+      </c>
+      <c r="I12" s="17">
+        <v>0.69764693455947124</v>
+      </c>
+      <c r="J12" s="17">
+        <v>-0.99237845448159268</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="17">
+        <v>10.8619952521514</v>
+      </c>
+      <c r="D13" s="17">
+        <v>2.5955168639584691</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0.68341524385114349</v>
+      </c>
+      <c r="G13" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="H13" s="17">
         <v>1.154061313732617</v>
       </c>
-      <c r="D4" s="17">
-        <v>0.2424674618526505</v>
-      </c>
-      <c r="E4" s="17">
-        <v>-1.371171399275058</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B5" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="17">
-        <v>1.322298040883372</v>
-      </c>
-      <c r="D5" s="17">
-        <v>0.28589805137132751</v>
-      </c>
-      <c r="E5" s="17">
-        <v>-1.320902128073866</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" s="17">
-        <v>2.7387698013796831</v>
-      </c>
-      <c r="D6" s="17">
-        <v>0.84577935351094191</v>
-      </c>
-      <c r="E6" s="17">
-        <v>-0.87540812914845312</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B7" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="17">
+      <c r="I13" s="17">
+        <v>0.24246746185265089</v>
+      </c>
+      <c r="J13" s="17">
+        <v>-1.3711713992750809</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" s="20">
+        <f>AVERAGE(C11:C13)</f>
+        <v>10.890995967945704</v>
+      </c>
+      <c r="D14" s="20">
+        <f>AVERAGE(D11:D13)</f>
+        <v>2.6174331887969893</v>
+      </c>
+      <c r="E14" s="20">
+        <f>AVERAGE(E11:E13)</f>
+        <v>0.70109553660437429</v>
+      </c>
+      <c r="G14" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" s="17">
+        <v>1.3222980408833731</v>
+      </c>
+      <c r="I14" s="17">
+        <v>0.28589805137132768</v>
+      </c>
+      <c r="J14" s="17">
+        <v>-1.3209021280739359</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="C15" s="18">
+        <f>MIN(C11:C13)</f>
+        <v>10.79532945823042</v>
+      </c>
+      <c r="D15" s="18">
+        <f>MIN(D11:D13)</f>
+        <v>2.581879576756648</v>
+      </c>
+      <c r="E15" s="18">
+        <f>MIN(E11:E13)</f>
+        <v>0.67639002643719903</v>
+      </c>
+      <c r="G15" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="17">
+        <v>2.7387698013796919</v>
+      </c>
+      <c r="I15" s="17">
+        <v>0.84577935351094302</v>
+      </c>
+      <c r="J15" s="17">
+        <v>-0.8754081291484449</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="18">
+        <f>MAX(C11:C13)</f>
+        <v>11.015663193455291</v>
+      </c>
+      <c r="D16" s="18">
+        <f>MAX(D11:D13)</f>
+        <v>2.6749031256758502</v>
+      </c>
+      <c r="E16" s="18">
+        <f>MAX(E11:E13)</f>
+        <v>0.74348133952478035</v>
+      </c>
+      <c r="G16" s="14" t="s">
+        <v>24</v>
+      </c>
+      <c r="H16" s="17">
         <v>1.6775179614556699</v>
       </c>
-      <c r="D7" s="17">
-        <v>0.3345958313526991</v>
-      </c>
-      <c r="E7" s="17">
-        <v>-1.2984237493742981</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="17">
-        <v>1.850332406227821</v>
-      </c>
-      <c r="D8" s="17">
-        <v>0.37883209916837801</v>
-      </c>
-      <c r="E8" s="17">
-        <v>-1.2475182875729991</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C9" s="20">
-        <f>AVERAGE(C3:C8)</f>
-        <v>1.7733479748638368</v>
-      </c>
-      <c r="D9" s="20">
-        <f>AVERAGE(D3:D8)</f>
-        <v>0.46420328863591104</v>
-      </c>
-      <c r="E9" s="20">
-        <f>AVERAGE(E3:E8)</f>
-        <v>-1.1843003579877118</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" s="18">
-        <f>MIN(C3:C8)</f>
+      <c r="I16" s="17">
+        <v>0.33459583135269971</v>
+      </c>
+      <c r="J16" s="17">
+        <v>-1.29842374937432</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G17" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="H17" s="17">
+        <v>1.8503324062278219</v>
+      </c>
+      <c r="I17" s="17">
+        <v>0.37883209916837851</v>
+      </c>
+      <c r="J17" s="17">
+        <v>-1.2475182875730371</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G18" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="H18" s="20">
+        <f>AVERAGE(H12:H17)</f>
+        <v>1.7733479748638399</v>
+      </c>
+      <c r="I18" s="20">
+        <f>AVERAGE(I12:I17)</f>
+        <v>0.46420328863591181</v>
+      </c>
+      <c r="J18" s="20">
+        <f>AVERAGE(J12:J17)</f>
+        <v>-1.1843003579877351</v>
+      </c>
+    </row>
+    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G19" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="18">
+        <f>MIN(H12:H17)</f>
         <v>1.154061313732617</v>
       </c>
-      <c r="D10" s="18">
-        <f>MIN(D3:D8)</f>
-        <v>0.2424674618526505</v>
-      </c>
-      <c r="E10" s="18">
-        <f>MIN(E3:E8)</f>
-        <v>-1.371171399275058</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="C11" s="18">
-        <f>MAX(C3:C8)</f>
-        <v>2.7387698013796831</v>
-      </c>
-      <c r="D11" s="18">
-        <f>MAX(D3:D8)</f>
-        <v>0.84577935351094191</v>
-      </c>
-      <c r="E11" s="18">
-        <f>MAX(E3:E8)</f>
-        <v>-0.87540812914845312</v>
+      <c r="I19" s="18">
+        <f>MIN(I12:I17)</f>
+        <v>0.24246746185265089</v>
+      </c>
+      <c r="J19" s="18">
+        <f>MIN(J12:J17)</f>
+        <v>-1.3711713992750809</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" s="18">
+        <f>MAX(H12:H17)</f>
+        <v>2.7387698013796919</v>
+      </c>
+      <c r="I20" s="18">
+        <f>MAX(I12:I17)</f>
+        <v>0.84577935351094302</v>
+      </c>
+      <c r="J20" s="18">
+        <f>MAX(J12:J17)</f>
+        <v>-0.8754081291484449</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B9:E9"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>